--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/91.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/91.xlsx
@@ -426,13 +426,13 @@
         <v>-4.221508789465944</v>
       </c>
       <c r="E2">
-        <v>-20.76808200802471</v>
+        <v>-22.97317714131971</v>
       </c>
       <c r="F2">
-        <v>-1.659403952618339</v>
+        <v>-1.352366261301091</v>
       </c>
       <c r="G2">
-        <v>-13.82306155971022</v>
+        <v>-13.9697154165544</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.039992633731741</v>
       </c>
       <c r="E3">
-        <v>-22.89702179393272</v>
+        <v>-23.40026205345711</v>
       </c>
       <c r="F3">
-        <v>-1.809193488229559</v>
+        <v>-1.03705732146689</v>
       </c>
       <c r="G3">
-        <v>-13.50964724768911</v>
+        <v>-12.62974562517007</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.866217869916514</v>
       </c>
       <c r="E4">
-        <v>-22.19999454619809</v>
+        <v>-24.65807287993159</v>
       </c>
       <c r="F4">
-        <v>-1.471120183799025</v>
+        <v>-1.074582364813708</v>
       </c>
       <c r="G4">
-        <v>-12.93140915579954</v>
+        <v>-13.704201387941</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-0.8169087311761395</v>
       </c>
       <c r="E5">
-        <v>-23.09760149315446</v>
+        <v>-24.91622759768686</v>
       </c>
       <c r="F5">
-        <v>-1.447109954628882</v>
+        <v>-0.9896291458196044</v>
       </c>
       <c r="G5">
-        <v>-12.43111620335934</v>
+        <v>-13.16148876023335</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>0.1362008878911866</v>
       </c>
       <c r="E6">
-        <v>-21.82596070706055</v>
+        <v>-25.33918707000327</v>
       </c>
       <c r="F6">
-        <v>-1.982245237246196</v>
+        <v>-1.297610347608641</v>
       </c>
       <c r="G6">
-        <v>-11.94556179965997</v>
+        <v>-12.95432806256791</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>0.9795547839597952</v>
       </c>
       <c r="E7">
-        <v>-23.30465691020717</v>
+        <v>-25.83516818569337</v>
       </c>
       <c r="F7">
-        <v>-1.545117415523702</v>
+        <v>-0.9894535319302108</v>
       </c>
       <c r="G7">
-        <v>-10.83498301923728</v>
+        <v>-12.46840949885923</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>1.72010986601456</v>
       </c>
       <c r="E8">
-        <v>-23.66712502672912</v>
+        <v>-26.21660607983345</v>
       </c>
       <c r="F8">
-        <v>-1.142372639589208</v>
+        <v>-1.182811879459074</v>
       </c>
       <c r="G8">
-        <v>-10.70629880358027</v>
+        <v>-11.87157110685726</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>2.34882600530629</v>
       </c>
       <c r="E9">
-        <v>-24.3420397358843</v>
+        <v>-26.62915911888024</v>
       </c>
       <c r="F9">
-        <v>-2.367045918501248</v>
+        <v>-0.9612650175803464</v>
       </c>
       <c r="G9">
-        <v>-10.2773083809649</v>
+        <v>-12.04150471993359</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>2.867649801682657</v>
       </c>
       <c r="E10">
-        <v>-25.2232490784589</v>
+        <v>-26.04498144341675</v>
       </c>
       <c r="F10">
-        <v>-1.471613890771094</v>
+        <v>-0.8995698701546448</v>
       </c>
       <c r="G10">
-        <v>-10.63253984896531</v>
+        <v>-11.31565105772069</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>3.263322095435274</v>
       </c>
       <c r="E11">
-        <v>-25.43869575784782</v>
+        <v>-27.23635502772471</v>
       </c>
       <c r="F11">
-        <v>-1.10526177994379</v>
+        <v>-1.030880185744214</v>
       </c>
       <c r="G11">
-        <v>-9.117637520740356</v>
+        <v>-11.57613140184162</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>3.529309240051459</v>
       </c>
       <c r="E12">
-        <v>-27.00153553653097</v>
+        <v>-28.4048462328719</v>
       </c>
       <c r="F12">
-        <v>-0.6151374968923926</v>
+        <v>-0.78234262878007</v>
       </c>
       <c r="G12">
-        <v>-9.074123710172175</v>
+        <v>-11.11005293754979</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>3.663468930431639</v>
       </c>
       <c r="E13">
-        <v>-25.9076871684522</v>
+        <v>-29.64831991063811</v>
       </c>
       <c r="F13">
-        <v>-0.761056899997734</v>
+        <v>-0.269926150551935</v>
       </c>
       <c r="G13">
-        <v>-9.242607304302304</v>
+        <v>-9.350445014698524</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>3.666458177680938</v>
       </c>
       <c r="E14">
-        <v>-27.12181180617469</v>
+        <v>-28.90706305727056</v>
       </c>
       <c r="F14">
-        <v>0.08994315698105977</v>
+        <v>-0.02502512648608082</v>
       </c>
       <c r="G14">
-        <v>-9.667979300643259</v>
+        <v>-9.23681053906304</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>3.551050911965119</v>
       </c>
       <c r="E15">
-        <v>-29.62094075678773</v>
+        <v>-28.7085981554104</v>
       </c>
       <c r="F15">
-        <v>-0.1881190709536643</v>
+        <v>0.1939993566511225</v>
       </c>
       <c r="G15">
-        <v>-8.649344301482751</v>
+        <v>-10.02909029752142</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.341097533669768</v>
       </c>
       <c r="E16">
-        <v>-28.08310268310093</v>
+        <v>-30.87871535547016</v>
       </c>
       <c r="F16">
-        <v>-0.3040623428538999</v>
+        <v>0.3917397677407953</v>
       </c>
       <c r="G16">
-        <v>-8.607502316411901</v>
+        <v>-9.235509494666108</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.066083142437798</v>
       </c>
       <c r="E17">
-        <v>-29.85391715906035</v>
+        <v>-31.16367637511383</v>
       </c>
       <c r="F17">
-        <v>0.7380644398706153</v>
+        <v>0.4941442028096757</v>
       </c>
       <c r="G17">
-        <v>-7.651992799594217</v>
+        <v>-9.424346322771674</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.75786067163595</v>
       </c>
       <c r="E18">
-        <v>-29.20701106164261</v>
+        <v>-33.15416259671132</v>
       </c>
       <c r="F18">
-        <v>0.8693706136231706</v>
+        <v>1.361911244388534</v>
       </c>
       <c r="G18">
-        <v>-7.637270803581077</v>
+        <v>-9.068247491839969</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.446877929648433</v>
       </c>
       <c r="E19">
-        <v>-30.47878317348275</v>
+        <v>-33.70367027517209</v>
       </c>
       <c r="F19">
-        <v>1.150808438724303</v>
+        <v>1.253582325654832</v>
       </c>
       <c r="G19">
-        <v>-7.023611529694074</v>
+        <v>-8.529356888957405</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.161633108875358</v>
       </c>
       <c r="E20">
-        <v>-30.91533486053319</v>
+        <v>-32.45260461073202</v>
       </c>
       <c r="F20">
-        <v>1.683680621597169</v>
+        <v>1.549432086829869</v>
       </c>
       <c r="G20">
-        <v>-8.198183155390874</v>
+        <v>-8.291120100314833</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.922259502223333</v>
       </c>
       <c r="E21">
-        <v>-32.53851655536854</v>
+        <v>-33.72488617589802</v>
       </c>
       <c r="F21">
-        <v>1.596304427949877</v>
+        <v>1.926108968965666</v>
       </c>
       <c r="G21">
-        <v>-7.522540537372095</v>
+        <v>-7.690491133670401</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.739308410399568</v>
       </c>
       <c r="E22">
-        <v>-32.16417704423548</v>
+        <v>-34.88995611893242</v>
       </c>
       <c r="F22">
-        <v>1.911991931687157</v>
+        <v>2.45244698976525</v>
       </c>
       <c r="G22">
-        <v>-7.499320370959647</v>
+        <v>-8.379260064752389</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.61917892256733</v>
       </c>
       <c r="E23">
-        <v>-32.27523107656258</v>
+        <v>-35.26558398092067</v>
       </c>
       <c r="F23">
-        <v>1.899818244335616</v>
+        <v>2.491650305470139</v>
       </c>
       <c r="G23">
-        <v>-6.931916039347341</v>
+        <v>-8.382603715747052</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.560214750366011</v>
       </c>
       <c r="E24">
-        <v>-32.78310622923383</v>
+        <v>-35.37847657369488</v>
       </c>
       <c r="F24">
-        <v>2.290600566606282</v>
+        <v>2.738913005001375</v>
       </c>
       <c r="G24">
-        <v>-7.53691823664915</v>
+        <v>-8.611077705594315</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.553131929856135</v>
       </c>
       <c r="E25">
-        <v>-33.08933975552853</v>
+        <v>-35.78372291993029</v>
       </c>
       <c r="F25">
-        <v>2.404323813867015</v>
+        <v>2.593305896406889</v>
       </c>
       <c r="G25">
-        <v>-7.603135768525652</v>
+        <v>-7.73914622146107</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.588959690054637</v>
       </c>
       <c r="E26">
-        <v>-33.49677561894664</v>
+        <v>-36.30898062007998</v>
       </c>
       <c r="F26">
-        <v>2.326916193545013</v>
+        <v>2.221486560721108</v>
       </c>
       <c r="G26">
-        <v>-7.979025040691121</v>
+        <v>-8.444702928972703</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.657113971472786</v>
       </c>
       <c r="E27">
-        <v>-32.50002679054035</v>
+        <v>-36.17441701494205</v>
       </c>
       <c r="F27">
-        <v>2.408629667626767</v>
+        <v>2.53196363349478</v>
       </c>
       <c r="G27">
-        <v>-7.819797731888794</v>
+        <v>-7.84493470416848</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.742820862782685</v>
       </c>
       <c r="E28">
-        <v>-33.56662280204095</v>
+        <v>-35.65682149281334</v>
       </c>
       <c r="F28">
-        <v>3.119047492676457</v>
+        <v>3.060496827911782</v>
       </c>
       <c r="G28">
-        <v>-6.952517564238225</v>
+        <v>-7.597077470188786</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.833853226238273</v>
       </c>
       <c r="E29">
-        <v>-33.23217914691547</v>
+        <v>-35.92230328151302</v>
       </c>
       <c r="F29">
-        <v>2.651604737481112</v>
+        <v>2.600648545065304</v>
       </c>
       <c r="G29">
-        <v>-7.901435784887222</v>
+        <v>-8.021072279585404</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.919887211356819</v>
       </c>
       <c r="E30">
-        <v>-33.22040511449553</v>
+        <v>-36.38013200368849</v>
       </c>
       <c r="F30">
-        <v>2.482713877928738</v>
+        <v>2.984007038672081</v>
       </c>
       <c r="G30">
-        <v>-7.769745593880553</v>
+        <v>-8.603983206503656</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.988720868403389</v>
       </c>
       <c r="E31">
-        <v>-33.49850549601758</v>
+        <v>-35.16626096051043</v>
       </c>
       <c r="F31">
-        <v>2.261309495243292</v>
+        <v>2.358326228724364</v>
       </c>
       <c r="G31">
-        <v>-8.020850473034272</v>
+        <v>-8.666847155748878</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.031433268980774</v>
       </c>
       <c r="E32">
-        <v>-32.24993728499274</v>
+        <v>-34.76976589029484</v>
       </c>
       <c r="F32">
-        <v>1.974137710979982</v>
+        <v>2.405389094347016</v>
       </c>
       <c r="G32">
-        <v>-8.104776113000337</v>
+        <v>-8.388824230815343</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.042916753346379</v>
       </c>
       <c r="E33">
-        <v>-32.23972784034245</v>
+        <v>-35.28091965814764</v>
       </c>
       <c r="F33">
-        <v>1.938168341615621</v>
+        <v>2.438580119442386</v>
       </c>
       <c r="G33">
-        <v>-7.435582437692059</v>
+        <v>-8.381024585524822</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.018060976722907</v>
       </c>
       <c r="E34">
-        <v>-31.81297803528162</v>
+        <v>-35.18045772652447</v>
       </c>
       <c r="F34">
-        <v>1.835828519204159</v>
+        <v>2.276702218322112</v>
       </c>
       <c r="G34">
-        <v>-8.023555188739858</v>
+        <v>-8.575515825411463</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.954724083523425</v>
       </c>
       <c r="E35">
-        <v>-30.02717657459382</v>
+        <v>-33.15567737126689</v>
       </c>
       <c r="F35">
-        <v>1.985471433785085</v>
+        <v>2.221011077831902</v>
       </c>
       <c r="G35">
-        <v>-7.808541877055272</v>
+        <v>-8.590347069427398</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.855180207524036</v>
       </c>
       <c r="E36">
-        <v>-30.56695256241209</v>
+        <v>-34.43006241260945</v>
       </c>
       <c r="F36">
-        <v>1.880775734480061</v>
+        <v>2.078929500903731</v>
       </c>
       <c r="G36">
-        <v>-7.898929701913993</v>
+        <v>-8.228762664537122</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.722993921505062</v>
       </c>
       <c r="E37">
-        <v>-29.8126763462725</v>
+        <v>-32.54359297473114</v>
       </c>
       <c r="F37">
-        <v>1.946148833174192</v>
+        <v>2.178789191311211</v>
       </c>
       <c r="G37">
-        <v>-7.90608048027882</v>
+        <v>-9.095211885257333</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>1.562652436586378</v>
       </c>
       <c r="E38">
-        <v>-28.8060101597894</v>
+        <v>-32.3034004491273</v>
       </c>
       <c r="F38">
-        <v>1.85899464199085</v>
+        <v>1.771186040559297</v>
       </c>
       <c r="G38">
-        <v>-7.737391632325256</v>
+        <v>-8.33387910650006</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>1.381175493314532</v>
       </c>
       <c r="E39">
-        <v>-29.11832089820239</v>
+        <v>-31.9527108934993</v>
       </c>
       <c r="F39">
-        <v>1.175589877946453</v>
+        <v>1.727650363337766</v>
       </c>
       <c r="G39">
-        <v>-7.360019235758194</v>
+        <v>-8.098469523748024</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>1.184690981779146</v>
       </c>
       <c r="E40">
-        <v>-28.52005514010105</v>
+        <v>-31.35202240180385</v>
       </c>
       <c r="F40">
-        <v>1.225432744572899</v>
+        <v>1.410642441960424</v>
       </c>
       <c r="G40">
-        <v>-8.181282820412894</v>
+        <v>-8.363352893436192</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>0.9770341166781188</v>
       </c>
       <c r="E41">
-        <v>-27.99207582707275</v>
+        <v>-31.27664821618318</v>
       </c>
       <c r="F41">
-        <v>1.340945265423679</v>
+        <v>1.787554580438615</v>
       </c>
       <c r="G41">
-        <v>-8.194210500743747</v>
+        <v>-7.449132500584295</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>0.7620451672404004</v>
       </c>
       <c r="E42">
-        <v>-27.2946817729435</v>
+        <v>-29.79997850515499</v>
       </c>
       <c r="F42">
-        <v>1.765702248352764</v>
+        <v>1.478204087332751</v>
       </c>
       <c r="G42">
-        <v>-7.903720061309319</v>
+        <v>-8.802963546141552</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.5433708088906424</v>
       </c>
       <c r="E43">
-        <v>-26.35058551182438</v>
+        <v>-30.93122754006311</v>
       </c>
       <c r="F43">
-        <v>1.224837976777689</v>
+        <v>1.529369028334066</v>
       </c>
       <c r="G43">
-        <v>-9.671432199640719</v>
+        <v>-7.531747164516808</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.3230654003168336</v>
       </c>
       <c r="E44">
-        <v>-25.97964914890809</v>
+        <v>-29.99542291485203</v>
       </c>
       <c r="F44">
-        <v>0.9159463992129756</v>
+        <v>1.709538938442958</v>
       </c>
       <c r="G44">
-        <v>-8.006730996309281</v>
+        <v>-8.050615587977861</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.103057178179868</v>
       </c>
       <c r="E45">
-        <v>-25.92761245408595</v>
+        <v>-29.47935348846391</v>
       </c>
       <c r="F45">
-        <v>1.031666011914455</v>
+        <v>1.700527957835305</v>
       </c>
       <c r="G45">
-        <v>-7.664827784649971</v>
+        <v>-8.510006750280365</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.1138903613371108</v>
       </c>
       <c r="E46">
-        <v>-25.49812292225048</v>
+        <v>-29.67178646294585</v>
       </c>
       <c r="F46">
-        <v>1.475859807582829</v>
+        <v>1.915176175983518</v>
       </c>
       <c r="G46">
-        <v>-7.860361846381484</v>
+        <v>-8.642405398032437</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.3263748259270592</v>
       </c>
       <c r="E47">
-        <v>-24.68212360538633</v>
+        <v>-28.62496629743675</v>
       </c>
       <c r="F47">
-        <v>0.8821175312174494</v>
+        <v>1.783884912844214</v>
       </c>
       <c r="G47">
-        <v>-8.4262665008645</v>
+        <v>-9.108364682684858</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.5348327791122274</v>
       </c>
       <c r="E48">
-        <v>-24.51694298748255</v>
+        <v>-28.27380125203794</v>
       </c>
       <c r="F48">
-        <v>1.081717627126407</v>
+        <v>1.502808255930702</v>
       </c>
       <c r="G48">
-        <v>-7.628375367717056</v>
+        <v>-7.761273907845558</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.7379047219535571</v>
       </c>
       <c r="E49">
-        <v>-24.59953782490845</v>
+        <v>-27.90988855230754</v>
       </c>
       <c r="F49">
-        <v>1.51509625798383</v>
+        <v>1.602204060592615</v>
       </c>
       <c r="G49">
-        <v>-7.710860920373537</v>
+        <v>-7.542744796798267</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.9336742876199403</v>
       </c>
       <c r="E50">
-        <v>-23.26462067150536</v>
+        <v>-27.61349992850552</v>
       </c>
       <c r="F50">
-        <v>1.447489880771751</v>
+        <v>1.364888396834196</v>
       </c>
       <c r="G50">
-        <v>-7.877331702815789</v>
+        <v>-7.327579200018875</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.12291088301197</v>
       </c>
       <c r="E51">
-        <v>-23.29818572085021</v>
+        <v>-25.65881582241266</v>
       </c>
       <c r="F51">
-        <v>0.9892950192612606</v>
+        <v>1.585944865210466</v>
       </c>
       <c r="G51">
-        <v>-8.560045646106449</v>
+        <v>-7.70925530578699</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.304388673825637</v>
       </c>
       <c r="E52">
-        <v>-23.63073420960348</v>
+        <v>-26.00573315919227</v>
       </c>
       <c r="F52">
-        <v>1.038037813976789</v>
+        <v>1.407483048686146</v>
       </c>
       <c r="G52">
-        <v>-7.825160815662414</v>
+        <v>-7.653373297084093</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.475691260196168</v>
       </c>
       <c r="E53">
-        <v>-22.52952254278824</v>
+        <v>-25.13515214511368</v>
       </c>
       <c r="F53">
-        <v>1.511714862245602</v>
+        <v>1.116729403773131</v>
       </c>
       <c r="G53">
-        <v>-8.001778420182532</v>
+        <v>-8.056395800489428</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.639272277346554</v>
       </c>
       <c r="E54">
-        <v>-21.76554633532422</v>
+        <v>-25.90661392011238</v>
       </c>
       <c r="F54">
-        <v>0.8463569104385947</v>
+        <v>1.85365664244721</v>
       </c>
       <c r="G54">
-        <v>-7.150617298762674</v>
+        <v>-7.913406717557226</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.796477346731288</v>
       </c>
       <c r="E55">
-        <v>-21.85131563302949</v>
+        <v>-23.92148941173997</v>
       </c>
       <c r="F55">
-        <v>0.6560328727061859</v>
+        <v>0.6513633656566051</v>
       </c>
       <c r="G55">
-        <v>-8.164968451995366</v>
+        <v>-7.538421224323979</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.946874522417877</v>
       </c>
       <c r="E56">
-        <v>-21.47835504223177</v>
+        <v>-24.26553569599871</v>
       </c>
       <c r="F56">
-        <v>0.6318230069919676</v>
+        <v>1.002316954833269</v>
       </c>
       <c r="G56">
-        <v>-7.307321971864075</v>
+        <v>-7.805807366439835</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.092354063068239</v>
       </c>
       <c r="E57">
-        <v>-21.43817842083572</v>
+        <v>-23.53022925747725</v>
       </c>
       <c r="F57">
-        <v>0.8592993227399341</v>
+        <v>1.416547044807578</v>
       </c>
       <c r="G57">
-        <v>-7.885382949567296</v>
+        <v>-8.384153051059432</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.233920186638698</v>
       </c>
       <c r="E58">
-        <v>-20.6717251380895</v>
+        <v>-23.20746227258054</v>
       </c>
       <c r="F58">
-        <v>0.6632206166602772</v>
+        <v>1.131307013327597</v>
       </c>
       <c r="G58">
-        <v>-7.723729010884684</v>
+        <v>-7.706169877344389</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.36937977168968</v>
       </c>
       <c r="E59">
-        <v>-21.22644509013308</v>
+        <v>-22.78874598040932</v>
       </c>
       <c r="F59">
-        <v>0.4428707456785947</v>
+        <v>0.4539808092849417</v>
       </c>
       <c r="G59">
-        <v>-8.110413972053715</v>
+        <v>-7.847007105676064</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.497159527231531</v>
       </c>
       <c r="E60">
-        <v>-20.42332022487275</v>
+        <v>-23.45659174163852</v>
       </c>
       <c r="F60">
-        <v>0.7261972484581096</v>
+        <v>1.009681141044156</v>
       </c>
       <c r="G60">
-        <v>-7.537295638840627</v>
+        <v>-8.324228866253085</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.616627210157423</v>
       </c>
       <c r="E61">
-        <v>-20.56995674171512</v>
+        <v>-22.27963681857099</v>
       </c>
       <c r="F61">
-        <v>0.09426309298665919</v>
+        <v>1.015802776150845</v>
       </c>
       <c r="G61">
-        <v>-6.9866062516561</v>
+        <v>-7.383534040723637</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.724636727847031</v>
       </c>
       <c r="E62">
-        <v>-19.61546310427439</v>
+        <v>-22.28383018550209</v>
       </c>
       <c r="F62">
-        <v>0.2537726917023292</v>
+        <v>0.921208188955558</v>
       </c>
       <c r="G62">
-        <v>-8.162571617024932</v>
+        <v>-8.276563631578657</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.817653904796787</v>
       </c>
       <c r="E63">
-        <v>-18.7516159310452</v>
+        <v>-22.26075761043301</v>
       </c>
       <c r="F63">
-        <v>0.4174017615121212</v>
+        <v>0.9774477086664221</v>
       </c>
       <c r="G63">
-        <v>-7.676934449687086</v>
+        <v>-8.742936734423486</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.894440525675054</v>
       </c>
       <c r="E64">
-        <v>-18.85523194481471</v>
+        <v>-20.78354221828689</v>
       </c>
       <c r="F64">
-        <v>0.3527261481711469</v>
+        <v>0.5610232734420966</v>
       </c>
       <c r="G64">
-        <v>-7.338748980668377</v>
+        <v>-8.805459697478161</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.952748342146138</v>
       </c>
       <c r="E65">
-        <v>-20.46035408530747</v>
+        <v>-21.93048241563159</v>
       </c>
       <c r="F65">
-        <v>-0.01825819317261166</v>
+        <v>1.031120946163413</v>
       </c>
       <c r="G65">
-        <v>-8.446176121737677</v>
+        <v>-7.967060729112195</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.98916447831339</v>
       </c>
       <c r="E66">
-        <v>-18.94270847722088</v>
+        <v>-20.72663741390651</v>
       </c>
       <c r="F66">
-        <v>0.1339046150476295</v>
+        <v>0.525564178397861</v>
       </c>
       <c r="G66">
-        <v>-8.629312190424621</v>
+        <v>-8.344416572951561</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.003464793025548</v>
       </c>
       <c r="E67">
-        <v>-20.03397561511527</v>
+        <v>-23.18198054933938</v>
       </c>
       <c r="F67">
-        <v>0.1222064105852949</v>
+        <v>0.4634374515553009</v>
       </c>
       <c r="G67">
-        <v>-8.443461474395475</v>
+        <v>-10.0519165090147</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.995545279221617</v>
       </c>
       <c r="E68">
-        <v>-19.10396290816001</v>
+        <v>-21.12937272130466</v>
       </c>
       <c r="F68">
-        <v>-0.1395783978844188</v>
+        <v>0.5203529190668493</v>
       </c>
       <c r="G68">
-        <v>-8.671587856961114</v>
+        <v>-8.710331171407205</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.963281028010978</v>
       </c>
       <c r="E69">
-        <v>-19.51265768735226</v>
+        <v>-21.23075619738838</v>
       </c>
       <c r="F69">
-        <v>0.0128155248412034</v>
+        <v>0.3997078337883237</v>
       </c>
       <c r="G69">
-        <v>-6.994531697677115</v>
+        <v>-8.685164404217664</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.906615624996342</v>
       </c>
       <c r="E70">
-        <v>-18.47843573653249</v>
+        <v>-21.38430316556646</v>
       </c>
       <c r="F70">
-        <v>0.2147093700885129</v>
+        <v>0.2304732017637875</v>
       </c>
       <c r="G70">
-        <v>-6.783203023177739</v>
+        <v>-8.725066409602501</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.8269952997641</v>
       </c>
       <c r="E71">
-        <v>-18.77680330347587</v>
+        <v>-21.8098166972232</v>
       </c>
       <c r="F71">
-        <v>0.03775435386988531</v>
+        <v>0.1889678530465183</v>
       </c>
       <c r="G71">
-        <v>-7.730369965236462</v>
+        <v>-8.932604509459411</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.723615394445784</v>
       </c>
       <c r="E72">
-        <v>-19.62029045756657</v>
+        <v>-22.33783223804356</v>
       </c>
       <c r="F72">
-        <v>-0.2980326565289223</v>
+        <v>0.1029170472437056</v>
       </c>
       <c r="G72">
-        <v>-6.812686741750489</v>
+        <v>-8.144707913295026</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.596011194508046</v>
       </c>
       <c r="E73">
-        <v>-19.01029142331135</v>
+        <v>-20.9980333896602</v>
       </c>
       <c r="F73">
-        <v>-0.2437994426676386</v>
+        <v>0.05044825595038494</v>
       </c>
       <c r="G73">
-        <v>-7.146389732109024</v>
+        <v>-8.606370109837471</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.446856617590126</v>
       </c>
       <c r="E74">
-        <v>-18.60746101795903</v>
+        <v>-21.59420699277</v>
       </c>
       <c r="F74">
-        <v>-0.1374188440653205</v>
+        <v>-0.1013144508143041</v>
       </c>
       <c r="G74">
-        <v>-7.157297979660923</v>
+        <v>-7.672134158655142</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.276352504079058</v>
       </c>
       <c r="E75">
-        <v>-18.05610119362914</v>
+        <v>-21.93008843839292</v>
       </c>
       <c r="F75">
-        <v>-0.04680042040347142</v>
+        <v>-0.2407792151170317</v>
       </c>
       <c r="G75">
-        <v>-6.555682470445788</v>
+        <v>-8.533120979235557</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.083241382849089</v>
       </c>
       <c r="E76">
-        <v>-20.25986495556588</v>
+        <v>-21.81275567685418</v>
       </c>
       <c r="F76">
-        <v>-0.5064664624213339</v>
+        <v>-0.5614733714368323</v>
       </c>
       <c r="G76">
-        <v>-6.707808659066377</v>
+        <v>-8.552414838638429</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.870014285224955</v>
       </c>
       <c r="E77">
-        <v>-19.46917527993061</v>
+        <v>-22.6695339021574</v>
       </c>
       <c r="F77">
-        <v>-0.2804629839155448</v>
+        <v>0.05807254952575159</v>
       </c>
       <c r="G77">
-        <v>-5.831000741353786</v>
+        <v>-8.281906852079041</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.637635008241256</v>
       </c>
       <c r="E78">
-        <v>-20.51898423828478</v>
+        <v>-22.48268906460092</v>
       </c>
       <c r="F78">
-        <v>-0.2265271539518662</v>
+        <v>-0.0279061883130175</v>
       </c>
       <c r="G78">
-        <v>-5.156059958989333</v>
+        <v>-7.594117842476678</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.384762462616738</v>
       </c>
       <c r="E79">
-        <v>-20.450626923139</v>
+        <v>-23.796938262633</v>
       </c>
       <c r="F79">
-        <v>-0.786354412111828</v>
+        <v>-0.4658408398858377</v>
       </c>
       <c r="G79">
-        <v>-5.474047789672949</v>
+        <v>-6.87059480432342</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.112968816901333</v>
       </c>
       <c r="E80">
-        <v>-21.22232870726011</v>
+        <v>-23.94078071101264</v>
       </c>
       <c r="F80">
-        <v>-0.6161820681873228</v>
+        <v>-0.4582347703933327</v>
       </c>
       <c r="G80">
-        <v>-4.934630810049641</v>
+        <v>-6.641644095918504</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.8236764319494855</v>
       </c>
       <c r="E81">
-        <v>-21.56336808477776</v>
+        <v>-24.50948006231791</v>
       </c>
       <c r="F81">
-        <v>-0.4705832432668649</v>
+        <v>-0.4177814482776188</v>
       </c>
       <c r="G81">
-        <v>-4.643872216426531</v>
+        <v>-5.94853835018007</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.5166517644815071</v>
       </c>
       <c r="E82">
-        <v>-24.64283456489579</v>
+        <v>-25.31208415306736</v>
       </c>
       <c r="F82">
-        <v>-0.5681036241288395</v>
+        <v>-0.5040567416465901</v>
       </c>
       <c r="G82">
-        <v>-4.463152845983256</v>
+        <v>-5.946522227946653</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.1932229426301861</v>
       </c>
       <c r="E83">
-        <v>-24.24265784531196</v>
+        <v>-25.60613608428143</v>
       </c>
       <c r="F83">
-        <v>-0.569192098896118</v>
+        <v>-0.5389658007353669</v>
       </c>
       <c r="G83">
-        <v>-3.832639584755823</v>
+        <v>-6.417649274185876</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.1431605551431136</v>
       </c>
       <c r="E84">
-        <v>-24.8622889437815</v>
+        <v>-26.8305222441053</v>
       </c>
       <c r="F84">
-        <v>-0.1102367961098576</v>
+        <v>-1.132700621794121</v>
       </c>
       <c r="G84">
-        <v>-3.708090240477362</v>
+        <v>-5.419145702449676</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.4896019590462912</v>
       </c>
       <c r="E85">
-        <v>-25.71505494111392</v>
+        <v>-27.27470214562166</v>
       </c>
       <c r="F85">
-        <v>-0.6532233449709055</v>
+        <v>-0.5481432831909826</v>
       </c>
       <c r="G85">
-        <v>-4.010362911486057</v>
+        <v>-6.039664426694049</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.8431824228427176</v>
       </c>
       <c r="E86">
-        <v>-26.75942520218488</v>
+        <v>-29.36711978865781</v>
       </c>
       <c r="F86">
-        <v>-0.5822380571228074</v>
+        <v>-0.3419344721424905</v>
       </c>
       <c r="G86">
-        <v>-4.210339725331273</v>
+        <v>-4.848252055838977</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.197520225425832</v>
       </c>
       <c r="E87">
-        <v>-28.19985127149268</v>
+        <v>-30.02284961767949</v>
       </c>
       <c r="F87">
-        <v>-1.034567249054075</v>
+        <v>-0.7326737193082117</v>
       </c>
       <c r="G87">
-        <v>-3.134743479622064</v>
+        <v>-4.388797993171226</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.545734869488034</v>
       </c>
       <c r="E88">
-        <v>-30.00421494713792</v>
+        <v>-31.6433504559023</v>
       </c>
       <c r="F88">
-        <v>-0.7335782965120687</v>
+        <v>-0.7473035160090538</v>
       </c>
       <c r="G88">
-        <v>-2.948892763592919</v>
+        <v>-4.426250194857</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.8825203666</v>
       </c>
       <c r="E89">
-        <v>-30.19694000819336</v>
+        <v>-33.52999650426692</v>
       </c>
       <c r="F89">
-        <v>-1.121523460428147</v>
+        <v>-1.119804598067338</v>
       </c>
       <c r="G89">
-        <v>-2.435850900280984</v>
+        <v>-4.941510123680247</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.198963910639841</v>
       </c>
       <c r="E90">
-        <v>-31.51689734771211</v>
+        <v>-34.43580451765118</v>
       </c>
       <c r="F90">
-        <v>-1.209570631671707</v>
+        <v>-1.100644460040586</v>
       </c>
       <c r="G90">
-        <v>-2.856879460874415</v>
+        <v>-4.64042262797461</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.484776592848057</v>
       </c>
       <c r="E91">
-        <v>-33.49963761451949</v>
+        <v>-36.20222863806016</v>
       </c>
       <c r="F91">
-        <v>-1.094734886989014</v>
+        <v>-1.133915836774028</v>
       </c>
       <c r="G91">
-        <v>-3.413683425669976</v>
+        <v>-5.112258130959236</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.731751151866285</v>
       </c>
       <c r="E92">
-        <v>-35.28618400918155</v>
+        <v>-38.12776522120264</v>
       </c>
       <c r="F92">
-        <v>-1.480152701959151</v>
+        <v>-1.188971619466291</v>
       </c>
       <c r="G92">
-        <v>-3.889693526579622</v>
+        <v>-4.716734013200351</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.929259235201171</v>
       </c>
       <c r="E93">
-        <v>-36.83394849789317</v>
+        <v>-38.93464645565234</v>
       </c>
       <c r="F93">
-        <v>-1.66144007969442</v>
+        <v>-1.358750488874467</v>
       </c>
       <c r="G93">
-        <v>-4.22747510904254</v>
+        <v>-4.8756766150863</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.066109909806459</v>
       </c>
       <c r="E94">
-        <v>-39.62834980346534</v>
+        <v>-40.87982303056609</v>
       </c>
       <c r="F94">
-        <v>-1.811126069380291</v>
+        <v>-1.376760024578731</v>
       </c>
       <c r="G94">
-        <v>-3.023542254957944</v>
+        <v>-4.617209082653241</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>3.136134840994816</v>
       </c>
       <c r="E95">
-        <v>-40.63524014941182</v>
+        <v>-43.71895433814903</v>
       </c>
       <c r="F95">
-        <v>-1.947368484486128</v>
+        <v>-1.813517566072173</v>
       </c>
       <c r="G95">
-        <v>-3.685005806432024</v>
+        <v>-5.306822202847743</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.128440196978871</v>
       </c>
       <c r="E96">
-        <v>-44.6371613133663</v>
+        <v>-45.69729972093197</v>
       </c>
       <c r="F96">
-        <v>-2.498436585728888</v>
+        <v>-1.445787051886611</v>
       </c>
       <c r="G96">
-        <v>-4.468863537038499</v>
+        <v>-5.758334266766783</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.044378106713225</v>
       </c>
       <c r="E97">
-        <v>-44.89482242745473</v>
+        <v>-47.36248301218847</v>
       </c>
       <c r="F97">
-        <v>-2.495997043727644</v>
+        <v>-1.940256121965692</v>
       </c>
       <c r="G97">
-        <v>-3.967792606396569</v>
+        <v>-6.260808868717364</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.868319154637781</v>
       </c>
       <c r="E98">
-        <v>-47.06293124929208</v>
+        <v>-49.81494603815246</v>
       </c>
       <c r="F98">
-        <v>-2.633460472385208</v>
+        <v>-2.390150742100131</v>
       </c>
       <c r="G98">
-        <v>-4.159850595311847</v>
+        <v>-6.786295072711419</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.620584155377363</v>
       </c>
       <c r="E99">
-        <v>-49.59999749090439</v>
+        <v>-51.82934033827346</v>
       </c>
       <c r="F99">
-        <v>-3.256655351757123</v>
+        <v>-2.483200424089197</v>
       </c>
       <c r="G99">
-        <v>-5.075828887845096</v>
+        <v>-7.311264831601347</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>2.270478858283576</v>
       </c>
       <c r="E100">
-        <v>-51.38399888317414</v>
+        <v>-54.64339295680192</v>
       </c>
       <c r="F100">
-        <v>-3.443269131892393</v>
+        <v>-2.991812210836274</v>
       </c>
       <c r="G100">
-        <v>-5.623604994955063</v>
+        <v>-7.249778069300463</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.869295497310146</v>
       </c>
       <c r="E101">
-        <v>-53.89712761118189</v>
+        <v>-55.66003989999792</v>
       </c>
       <c r="F101">
-        <v>-4.163786412317014</v>
+        <v>-3.093656669540862</v>
       </c>
       <c r="G101">
-        <v>-6.026356033626178</v>
+        <v>-8.068144926608301</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.33806690049878</v>
       </c>
       <c r="E102">
-        <v>-55.68580578498306</v>
+        <v>-58.26201615591766</v>
       </c>
       <c r="F102">
-        <v>-4.031615422995936</v>
+        <v>-2.913471848818719</v>
       </c>
       <c r="G102">
-        <v>-7.347889396902304</v>
+        <v>-8.997405127845106</v>
       </c>
     </row>
   </sheetData>
